--- a/accountant_forms/032_mileage_log_and_expense_report--accountant_forms.xlsx
+++ b/accountant_forms/032_mileage_log_and_expense_report--accountant_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rate</t>
+          <t>Expense Rate</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date (2)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rate</t>
+          <t>Rate (3)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_0.25}</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 0.25}</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_0.5}</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 0.5}</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_0.75}</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 0.75}</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'car'}</t>
+          <t>car</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Car'}</t>
+          <t>Car</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'gas'}</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Gas'}</t>
+          <t>Gas</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'meals'}</t>
+          <t>meals</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Meals'}</t>
+          <t>Meals</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'food'}</t>
+          <t>food</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Food'}</t>
+          <t>Food</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'transportation'}</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Transportation'}</t>
+          <t>Transportation</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_0.25}</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 0.25}</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_0.5}</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 0.5}</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_0.75}</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 0.75}</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'reimbursed'}</t>
+          <t>reimbursed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Reimbursed'}</t>
+          <t>Reimbursed</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
